--- a/artfynd/A 1728-2026 artfynd.xlsx
+++ b/artfynd/A 1728-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>6197088</v>
       </c>
       <c r="B2" t="n">
-        <v>95526</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>709222.7913051172</v>
+        <v>709223</v>
       </c>
       <c r="R2" t="n">
-        <v>7277629.355227097</v>
+        <v>7277629</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,19 +739,9 @@
           <t>2012-07-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-07-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>6199446</v>
       </c>
       <c r="B3" t="n">
-        <v>95513</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,17 +792,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Groddlummer</t>
+          <t>Gul groddlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago subsp. arctica</t>
+          <t>Huperzia arctica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Grossh. ex Tolm.) Á. Löve &amp; D. Löve</t>
+          <t>(Grossh. ex Tolm.) Sipliv.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>709555.3183322761</v>
+        <v>709555</v>
       </c>
       <c r="R3" t="n">
-        <v>7277450.526593307</v>
+        <v>7277451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2012-07-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-07-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 1728-2026 artfynd.xlsx
+++ b/artfynd/A 1728-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6197088</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,8 +890,17 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6199446</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>